--- a/output/yearly_population_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_19_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6120</v>
+        <v>5474</v>
       </c>
       <c r="C2" t="n">
-        <v>5584</v>
+        <v>6468</v>
       </c>
       <c r="D2" t="n">
-        <v>31443</v>
+        <v>23232</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3266</v>
+        <v>3209</v>
       </c>
       <c r="C3" t="n">
-        <v>3662</v>
+        <v>6691</v>
       </c>
       <c r="D3" t="n">
-        <v>15532</v>
+        <v>10856</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2581</v>
+        <v>2555</v>
       </c>
       <c r="C4" t="n">
-        <v>3959</v>
+        <v>7817</v>
       </c>
       <c r="D4" t="n">
-        <v>7413</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>1648</v>
       </c>
       <c r="C5" t="n">
-        <v>3362</v>
+        <v>6159</v>
       </c>
       <c r="D5" t="n">
-        <v>2729</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1067</v>
+        <v>911</v>
       </c>
       <c r="C6" t="n">
-        <v>2507</v>
+        <v>4347</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>982</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>417</v>
       </c>
       <c r="C7" t="n">
-        <v>1491</v>
+        <v>3097</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>612</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>568</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6865</v>
+        <v>6188</v>
       </c>
       <c r="C2" t="n">
-        <v>9740</v>
+        <v>6988</v>
       </c>
       <c r="D2" t="n">
-        <v>32261</v>
+        <v>19224</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3691</v>
+        <v>3375</v>
       </c>
       <c r="C3" t="n">
-        <v>4010</v>
+        <v>5836</v>
       </c>
       <c r="D3" t="n">
-        <v>16754</v>
+        <v>11727</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2471</v>
+        <v>2415</v>
       </c>
       <c r="C4" t="n">
-        <v>3728</v>
+        <v>7146</v>
       </c>
       <c r="D4" t="n">
-        <v>8590</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1876</v>
+        <v>1801</v>
       </c>
       <c r="C5" t="n">
-        <v>3546</v>
+        <v>6688</v>
       </c>
       <c r="D5" t="n">
-        <v>3384</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1263</v>
+        <v>1095</v>
       </c>
       <c r="C6" t="n">
-        <v>2883</v>
+        <v>5029</v>
       </c>
       <c r="D6" t="n">
-        <v>1396</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>677</v>
+        <v>548</v>
       </c>
       <c r="C7" t="n">
-        <v>1943</v>
+        <v>3622</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="C8" t="n">
-        <v>1008</v>
+        <v>2133</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>937</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7571</v>
+        <v>8556</v>
       </c>
       <c r="C2" t="n">
-        <v>9339</v>
+        <v>9786</v>
       </c>
       <c r="D2" t="n">
-        <v>26380</v>
+        <v>29161</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4083</v>
+        <v>3601</v>
       </c>
       <c r="C3" t="n">
-        <v>5741</v>
+        <v>5597</v>
       </c>
       <c r="D3" t="n">
-        <v>17639</v>
+        <v>11834</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2364</v>
       </c>
       <c r="C4" t="n">
-        <v>3780</v>
+        <v>6400</v>
       </c>
       <c r="D4" t="n">
-        <v>9500</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1892</v>
+        <v>1814</v>
       </c>
       <c r="C5" t="n">
-        <v>3518</v>
+        <v>6664</v>
       </c>
       <c r="D5" t="n">
-        <v>4080</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1388</v>
+        <v>1237</v>
       </c>
       <c r="C6" t="n">
-        <v>3142</v>
+        <v>5574</v>
       </c>
       <c r="D6" t="n">
-        <v>1650</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>826</v>
+        <v>673</v>
       </c>
       <c r="C7" t="n">
-        <v>2319</v>
+        <v>4158</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>402</v>
+        <v>302</v>
       </c>
       <c r="C8" t="n">
-        <v>1382</v>
+        <v>2651</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>1349</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>554</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6866</v>
+        <v>7709</v>
       </c>
       <c r="C2" t="n">
-        <v>6201</v>
+        <v>6889</v>
       </c>
       <c r="D2" t="n">
-        <v>21570</v>
+        <v>24010</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4862</v>
+        <v>4223</v>
       </c>
       <c r="C3" t="n">
-        <v>8232</v>
+        <v>9138</v>
       </c>
       <c r="D3" t="n">
-        <v>19294</v>
+        <v>12621</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1748</v>
+        <v>1676</v>
       </c>
       <c r="C4" t="n">
-        <v>5554</v>
+        <v>9715</v>
       </c>
       <c r="D4" t="n">
-        <v>9073</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1282</v>
+        <v>1142</v>
       </c>
       <c r="C5" t="n">
-        <v>3079</v>
+        <v>5462</v>
       </c>
       <c r="D5" t="n">
-        <v>2752</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>2272</v>
+        <v>4074</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>1354</v>
+        <v>2597</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>642</v>
+        <v>1322</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>542</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>159</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4177</v>
+        <v>4483</v>
       </c>
       <c r="C2" t="n">
-        <v>2645</v>
+        <v>3357</v>
       </c>
       <c r="D2" t="n">
-        <v>14711</v>
+        <v>16801</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4958</v>
+        <v>4790</v>
       </c>
       <c r="C3" t="n">
-        <v>6580</v>
+        <v>7437</v>
       </c>
       <c r="D3" t="n">
-        <v>18664</v>
+        <v>13372</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2578</v>
+        <v>2250</v>
       </c>
       <c r="C4" t="n">
-        <v>6883</v>
+        <v>9537</v>
       </c>
       <c r="D4" t="n">
-        <v>10454</v>
+        <v>6694</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1408</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="n">
-        <v>4231</v>
+        <v>7284</v>
       </c>
       <c r="D5" t="n">
-        <v>3597</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>733</v>
       </c>
       <c r="C6" t="n">
-        <v>2704</v>
+        <v>4777</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>1720</v>
+        <v>3161</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>867</v>
+        <v>1712</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>564</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5473</v>
+        <v>3951</v>
       </c>
       <c r="C2" t="n">
-        <v>8396</v>
+        <v>8489</v>
       </c>
       <c r="D2" t="n">
-        <v>14069</v>
+        <v>15613</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>3919</v>
       </c>
       <c r="C3" t="n">
-        <v>4111</v>
+        <v>4983</v>
       </c>
       <c r="D3" t="n">
-        <v>16810</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3134</v>
+        <v>2840</v>
       </c>
       <c r="C4" t="n">
-        <v>6585</v>
+        <v>8350</v>
       </c>
       <c r="D4" t="n">
-        <v>11554</v>
+        <v>7451</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1698</v>
+        <v>1475</v>
       </c>
       <c r="C5" t="n">
-        <v>5441</v>
+        <v>8149</v>
       </c>
       <c r="D5" t="n">
-        <v>4606</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1039</v>
+        <v>862</v>
       </c>
       <c r="C6" t="n">
-        <v>3421</v>
+        <v>5861</v>
       </c>
       <c r="D6" t="n">
-        <v>1386</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>514</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>2179</v>
+        <v>3855</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>2281</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>559</v>
+        <v>974</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3158</v>
+        <v>2382</v>
       </c>
       <c r="C2" t="n">
-        <v>3800</v>
+        <v>4148</v>
       </c>
       <c r="D2" t="n">
-        <v>9707</v>
+        <v>10902</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4132</v>
+        <v>3791</v>
       </c>
       <c r="C3" t="n">
-        <v>5481</v>
+        <v>5969</v>
       </c>
       <c r="D3" t="n">
-        <v>16099</v>
+        <v>13039</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3481</v>
+        <v>3120</v>
       </c>
       <c r="C4" t="n">
-        <v>6225</v>
+        <v>7943</v>
       </c>
       <c r="D4" t="n">
-        <v>12261</v>
+        <v>8123</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1804</v>
+        <v>1525</v>
       </c>
       <c r="C5" t="n">
-        <v>6423</v>
+        <v>9651</v>
       </c>
       <c r="D5" t="n">
-        <v>5001</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>689</v>
       </c>
       <c r="C6" t="n">
-        <v>4310</v>
+        <v>6803</v>
       </c>
       <c r="D6" t="n">
-        <v>1360</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>2305</v>
+        <v>4080</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>1602</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3201</v>
+        <v>2413</v>
       </c>
       <c r="C2" t="n">
-        <v>8315</v>
+        <v>11298</v>
       </c>
       <c r="D2" t="n">
-        <v>16427</v>
+        <v>15815</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3163</v>
+        <v>2764</v>
       </c>
       <c r="C3" t="n">
-        <v>4159</v>
+        <v>4572</v>
       </c>
       <c r="D3" t="n">
-        <v>14225</v>
+        <v>11910</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3311</v>
+        <v>2981</v>
       </c>
       <c r="C4" t="n">
-        <v>5731</v>
+        <v>6944</v>
       </c>
       <c r="D4" t="n">
-        <v>12514</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2214</v>
+        <v>1890</v>
       </c>
       <c r="C5" t="n">
-        <v>6257</v>
+        <v>8805</v>
       </c>
       <c r="D5" t="n">
-        <v>5964</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1151</v>
+        <v>893</v>
       </c>
       <c r="C6" t="n">
-        <v>5286</v>
+        <v>7958</v>
       </c>
       <c r="D6" t="n">
-        <v>1879</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>3151</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1492</v>
+        <v>2482</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>735</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
         <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2400</v>
+        <v>1671</v>
       </c>
       <c r="C2" t="n">
-        <v>4587</v>
+        <v>7069</v>
       </c>
       <c r="D2" t="n">
-        <v>12982</v>
+        <v>11502</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2780</v>
+        <v>2332</v>
       </c>
       <c r="C3" t="n">
-        <v>5362</v>
+        <v>6519</v>
       </c>
       <c r="D3" t="n">
-        <v>13846</v>
+        <v>11718</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3006</v>
+        <v>2665</v>
       </c>
       <c r="C4" t="n">
-        <v>5112</v>
+        <v>6022</v>
       </c>
       <c r="D4" t="n">
-        <v>12483</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2436</v>
+        <v>2087</v>
       </c>
       <c r="C5" t="n">
-        <v>6110</v>
+        <v>8316</v>
       </c>
       <c r="D5" t="n">
-        <v>6651</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1352</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>5823</v>
+        <v>8540</v>
       </c>
       <c r="D6" t="n">
-        <v>2246</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>3930</v>
+        <v>6175</v>
       </c>
       <c r="D7" t="n">
-        <v>772</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1944</v>
+        <v>3115</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>801</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4318</v>
+        <v>2456</v>
       </c>
       <c r="C2" t="n">
-        <v>4869</v>
+        <v>8322</v>
       </c>
       <c r="D2" t="n">
-        <v>13415</v>
+        <v>17863</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2221</v>
+        <v>1779</v>
       </c>
       <c r="C3" t="n">
-        <v>4504</v>
+        <v>6061</v>
       </c>
       <c r="D3" t="n">
-        <v>12827</v>
+        <v>10962</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2541</v>
+        <v>2219</v>
       </c>
       <c r="C4" t="n">
-        <v>5116</v>
+        <v>6097</v>
       </c>
       <c r="D4" t="n">
-        <v>12312</v>
+        <v>8974</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2404</v>
+        <v>2095</v>
       </c>
       <c r="C5" t="n">
-        <v>5561</v>
+        <v>7262</v>
       </c>
       <c r="D5" t="n">
-        <v>7288</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1617</v>
+        <v>1259</v>
       </c>
       <c r="C6" t="n">
-        <v>5887</v>
+        <v>8389</v>
       </c>
       <c r="D6" t="n">
-        <v>2808</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>4708</v>
+        <v>7006</v>
       </c>
       <c r="D7" t="n">
-        <v>951</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>2663</v>
+        <v>4163</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1068</v>
+        <v>1503</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5878</v>
+        <v>4137</v>
       </c>
       <c r="C2" t="n">
-        <v>2874</v>
+        <v>17826</v>
       </c>
       <c r="D2" t="n">
-        <v>7384</v>
+        <v>7156</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3055</v>
+        <v>1794</v>
       </c>
       <c r="C2" t="n">
-        <v>2726</v>
+        <v>4926</v>
       </c>
       <c r="D2" t="n">
-        <v>9874</v>
+        <v>13291</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3086</v>
+        <v>2429</v>
       </c>
       <c r="C3" t="n">
-        <v>4973</v>
+        <v>7142</v>
       </c>
       <c r="D3" t="n">
-        <v>13881</v>
+        <v>12213</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3518</v>
+        <v>3069</v>
       </c>
       <c r="C4" t="n">
-        <v>7085</v>
+        <v>8700</v>
       </c>
       <c r="D4" t="n">
-        <v>12789</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1582</v>
+        <v>1182</v>
       </c>
       <c r="C5" t="n">
-        <v>8183</v>
+        <v>11272</v>
       </c>
       <c r="D5" t="n">
-        <v>6693</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>564</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>5883</v>
+        <v>8345</v>
       </c>
       <c r="D6" t="n">
-        <v>2177</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2609</v>
+        <v>4079</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1046</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6930</v>
+        <v>7498</v>
       </c>
       <c r="C2" t="n">
-        <v>4294</v>
+        <v>8622</v>
       </c>
       <c r="D2" t="n">
-        <v>15420</v>
+        <v>10606</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2497</v>
+        <v>1759</v>
       </c>
       <c r="C3" t="n">
-        <v>1471</v>
+        <v>8984</v>
       </c>
       <c r="D3" t="n">
-        <v>1938</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5220</v>
+        <v>4748</v>
       </c>
       <c r="C2" t="n">
-        <v>8578</v>
+        <v>9238</v>
       </c>
       <c r="D2" t="n">
-        <v>21155</v>
+        <v>13899</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3869</v>
+        <v>3793</v>
       </c>
       <c r="C3" t="n">
-        <v>2666</v>
+        <v>7571</v>
       </c>
       <c r="D3" t="n">
-        <v>4060</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1118</v>
+        <v>798</v>
       </c>
       <c r="C4" t="n">
-        <v>919</v>
+        <v>5307</v>
       </c>
       <c r="D4" t="n">
-        <v>1571</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4729</v>
+        <v>4489</v>
       </c>
       <c r="C2" t="n">
-        <v>5512</v>
+        <v>8605</v>
       </c>
       <c r="D2" t="n">
-        <v>24380</v>
+        <v>11434</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3727</v>
+        <v>3503</v>
       </c>
       <c r="C3" t="n">
-        <v>5098</v>
+        <v>7339</v>
       </c>
       <c r="D3" t="n">
-        <v>6502</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2110</v>
+        <v>1911</v>
       </c>
       <c r="C4" t="n">
-        <v>1880</v>
+        <v>6457</v>
       </c>
       <c r="D4" t="n">
-        <v>2001</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>519</v>
+        <v>383</v>
       </c>
       <c r="C5" t="n">
-        <v>604</v>
+        <v>2950</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5170</v>
+        <v>5116</v>
       </c>
       <c r="C2" t="n">
-        <v>3562</v>
+        <v>5055</v>
       </c>
       <c r="D2" t="n">
-        <v>29580</v>
+        <v>17942</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>3263</v>
       </c>
       <c r="C3" t="n">
-        <v>4617</v>
+        <v>6956</v>
       </c>
       <c r="D3" t="n">
-        <v>8761</v>
+        <v>5364</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2463</v>
+        <v>2284</v>
       </c>
       <c r="C4" t="n">
-        <v>3601</v>
+        <v>6788</v>
       </c>
       <c r="D4" t="n">
-        <v>2741</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1095</v>
+        <v>918</v>
       </c>
       <c r="C5" t="n">
-        <v>1265</v>
+        <v>4644</v>
       </c>
       <c r="D5" t="n">
-        <v>1315</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="C6" t="n">
-        <v>449</v>
+        <v>1623</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>284</v>
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5529</v>
+        <v>6331</v>
       </c>
       <c r="C2" t="n">
-        <v>6449</v>
+        <v>17204</v>
       </c>
       <c r="D2" t="n">
-        <v>25413</v>
+        <v>19603</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3137</v>
+        <v>3008</v>
       </c>
       <c r="C3" t="n">
-        <v>3329</v>
+        <v>4941</v>
       </c>
       <c r="D3" t="n">
-        <v>10638</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1851</v>
+        <v>1713</v>
       </c>
       <c r="C4" t="n">
-        <v>3420</v>
+        <v>5568</v>
       </c>
       <c r="D4" t="n">
-        <v>3255</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>927</v>
+        <v>813</v>
       </c>
       <c r="C5" t="n">
-        <v>1823</v>
+        <v>4179</v>
       </c>
       <c r="D5" t="n">
-        <v>1244</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>585</v>
+        <v>2067</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>257</v>
+        <v>614</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4964</v>
+        <v>5073</v>
       </c>
       <c r="C2" t="n">
-        <v>5088</v>
+        <v>8432</v>
       </c>
       <c r="D2" t="n">
-        <v>32243</v>
+        <v>23245</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3617</v>
+        <v>3838</v>
       </c>
       <c r="C3" t="n">
-        <v>4472</v>
+        <v>10335</v>
       </c>
       <c r="D3" t="n">
-        <v>12438</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2200</v>
+        <v>2036</v>
       </c>
       <c r="C4" t="n">
-        <v>3292</v>
+        <v>5078</v>
       </c>
       <c r="D4" t="n">
-        <v>4715</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1248</v>
+        <v>1120</v>
       </c>
       <c r="C5" t="n">
-        <v>2750</v>
+        <v>4892</v>
       </c>
       <c r="D5" t="n">
-        <v>1599</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>582</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>1302</v>
+        <v>3218</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>446</v>
+        <v>1411</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>428</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4454</v>
+        <v>4192</v>
       </c>
       <c r="C2" t="n">
-        <v>4254</v>
+        <v>6992</v>
       </c>
       <c r="D2" t="n">
-        <v>26932</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3526</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>4159</v>
+        <v>8210</v>
       </c>
       <c r="D3" t="n">
-        <v>14711</v>
+        <v>9865</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2496</v>
+        <v>2473</v>
       </c>
       <c r="C4" t="n">
-        <v>3903</v>
+        <v>7749</v>
       </c>
       <c r="D4" t="n">
-        <v>6009</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1529</v>
+        <v>1377</v>
       </c>
       <c r="C5" t="n">
-        <v>2968</v>
+        <v>4888</v>
       </c>
       <c r="D5" t="n">
-        <v>2148</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>832</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>2078</v>
+        <v>4034</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>907</v>
+        <v>2299</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>347</v>
+        <v>909</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>223</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_19_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5474</v>
+        <v>6213</v>
       </c>
       <c r="C2" t="n">
-        <v>6468</v>
+        <v>5174</v>
       </c>
       <c r="D2" t="n">
-        <v>23232</v>
+        <v>25444</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3209</v>
+        <v>4053</v>
       </c>
       <c r="C3" t="n">
-        <v>6691</v>
+        <v>5273</v>
       </c>
       <c r="D3" t="n">
-        <v>10856</v>
+        <v>17333</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2555</v>
+        <v>3084</v>
       </c>
       <c r="C4" t="n">
-        <v>7817</v>
+        <v>6456</v>
       </c>
       <c r="D4" t="n">
-        <v>4719</v>
+        <v>7841</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1648</v>
+        <v>2085</v>
       </c>
       <c r="C5" t="n">
-        <v>6159</v>
+        <v>5059</v>
       </c>
       <c r="D5" t="n">
-        <v>1943</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>911</v>
+        <v>1194</v>
       </c>
       <c r="C6" t="n">
-        <v>4347</v>
+        <v>2760</v>
       </c>
       <c r="D6" t="n">
-        <v>982</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>558</v>
       </c>
       <c r="C7" t="n">
-        <v>3097</v>
+        <v>1212</v>
       </c>
       <c r="D7" t="n">
-        <v>627</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>1512</v>
+        <v>496</v>
       </c>
       <c r="D8" t="n">
-        <v>419</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
         <v>243</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6188</v>
+        <v>9328</v>
       </c>
       <c r="C2" t="n">
-        <v>6988</v>
+        <v>6327</v>
       </c>
       <c r="D2" t="n">
-        <v>19224</v>
+        <v>26422</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3375</v>
+        <v>4090</v>
       </c>
       <c r="C3" t="n">
-        <v>5836</v>
+        <v>4600</v>
       </c>
       <c r="D3" t="n">
-        <v>11727</v>
+        <v>17271</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2415</v>
+        <v>3026</v>
       </c>
       <c r="C4" t="n">
-        <v>7146</v>
+        <v>5753</v>
       </c>
       <c r="D4" t="n">
-        <v>5518</v>
+        <v>9151</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1801</v>
+        <v>2226</v>
       </c>
       <c r="C5" t="n">
-        <v>6688</v>
+        <v>5548</v>
       </c>
       <c r="D5" t="n">
-        <v>2265</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>1435</v>
       </c>
       <c r="C6" t="n">
-        <v>5029</v>
+        <v>3770</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>548</v>
+        <v>749</v>
       </c>
       <c r="C7" t="n">
-        <v>3622</v>
+        <v>1882</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>312</v>
       </c>
       <c r="C8" t="n">
-        <v>2133</v>
+        <v>804</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>937</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8556</v>
+        <v>12405</v>
       </c>
       <c r="C2" t="n">
-        <v>9786</v>
+        <v>6206</v>
       </c>
       <c r="D2" t="n">
-        <v>29161</v>
+        <v>25182</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3601</v>
+        <v>4996</v>
       </c>
       <c r="C3" t="n">
-        <v>5597</v>
+        <v>4712</v>
       </c>
       <c r="D3" t="n">
-        <v>11834</v>
+        <v>17475</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2364</v>
+        <v>2948</v>
       </c>
       <c r="C4" t="n">
-        <v>6400</v>
+        <v>5124</v>
       </c>
       <c r="D4" t="n">
-        <v>6131</v>
+        <v>9954</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1814</v>
+        <v>2270</v>
       </c>
       <c r="C5" t="n">
-        <v>6664</v>
+        <v>5465</v>
       </c>
       <c r="D5" t="n">
-        <v>2611</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>1615</v>
       </c>
       <c r="C6" t="n">
-        <v>5574</v>
+        <v>4470</v>
       </c>
       <c r="D6" t="n">
-        <v>1248</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>673</v>
+        <v>914</v>
       </c>
       <c r="C7" t="n">
-        <v>4158</v>
+        <v>2621</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>843</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>302</v>
+        <v>424</v>
       </c>
       <c r="C8" t="n">
-        <v>2651</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C9" t="n">
-        <v>1349</v>
+        <v>525</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>554</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7709</v>
+        <v>10999</v>
       </c>
       <c r="C2" t="n">
-        <v>6889</v>
+        <v>4220</v>
       </c>
       <c r="D2" t="n">
-        <v>24010</v>
+        <v>20816</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4223</v>
+        <v>5704</v>
       </c>
       <c r="C3" t="n">
-        <v>9138</v>
+        <v>7334</v>
       </c>
       <c r="D3" t="n">
-        <v>12621</v>
+        <v>19162</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1676</v>
+        <v>2097</v>
       </c>
       <c r="C4" t="n">
-        <v>9715</v>
+        <v>8099</v>
       </c>
       <c r="D4" t="n">
-        <v>5773</v>
+        <v>9479</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1142</v>
+        <v>1492</v>
       </c>
       <c r="C5" t="n">
-        <v>5462</v>
+        <v>4380</v>
       </c>
       <c r="D5" t="n">
-        <v>1899</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>621</v>
+        <v>844</v>
       </c>
       <c r="C6" t="n">
-        <v>4074</v>
+        <v>2568</v>
       </c>
       <c r="D6" t="n">
-        <v>691</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>2597</v>
+        <v>1193</v>
       </c>
       <c r="D7" t="n">
-        <v>456</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1322</v>
+        <v>514</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>542</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4483</v>
+        <v>6398</v>
       </c>
       <c r="C2" t="n">
-        <v>3357</v>
+        <v>1810</v>
       </c>
       <c r="D2" t="n">
-        <v>16801</v>
+        <v>14374</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4790</v>
+        <v>6766</v>
       </c>
       <c r="C3" t="n">
-        <v>7437</v>
+        <v>5346</v>
       </c>
       <c r="D3" t="n">
-        <v>13372</v>
+        <v>18283</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>3040</v>
       </c>
       <c r="C4" t="n">
-        <v>9537</v>
+        <v>7881</v>
       </c>
       <c r="D4" t="n">
-        <v>6694</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="n">
-        <v>7284</v>
+        <v>6034</v>
       </c>
       <c r="D5" t="n">
-        <v>2324</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>733</v>
+        <v>1012</v>
       </c>
       <c r="C6" t="n">
-        <v>4777</v>
+        <v>3325</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
-        <v>3161</v>
+        <v>1675</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>1712</v>
+        <v>700</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3951</v>
+        <v>6990</v>
       </c>
       <c r="C2" t="n">
-        <v>8489</v>
+        <v>6187</v>
       </c>
       <c r="D2" t="n">
-        <v>15613</v>
+        <v>21631</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3919</v>
+        <v>5544</v>
       </c>
       <c r="C3" t="n">
-        <v>4983</v>
+        <v>3216</v>
       </c>
       <c r="D3" t="n">
-        <v>13068</v>
+        <v>16637</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2840</v>
+        <v>4001</v>
       </c>
       <c r="C4" t="n">
-        <v>8350</v>
+        <v>6527</v>
       </c>
       <c r="D4" t="n">
-        <v>7451</v>
+        <v>11741</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1475</v>
+        <v>1975</v>
       </c>
       <c r="C5" t="n">
-        <v>8149</v>
+        <v>6777</v>
       </c>
       <c r="D5" t="n">
-        <v>2924</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>862</v>
+        <v>1169</v>
       </c>
       <c r="C6" t="n">
-        <v>5861</v>
+        <v>4514</v>
       </c>
       <c r="D6" t="n">
-        <v>1014</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>549</v>
       </c>
       <c r="C7" t="n">
-        <v>3855</v>
+        <v>2418</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>2281</v>
+        <v>1107</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>974</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2382</v>
+        <v>4135</v>
       </c>
       <c r="C2" t="n">
-        <v>4148</v>
+        <v>2841</v>
       </c>
       <c r="D2" t="n">
-        <v>10902</v>
+        <v>14952</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3791</v>
+        <v>5683</v>
       </c>
       <c r="C3" t="n">
-        <v>5969</v>
+        <v>4135</v>
       </c>
       <c r="D3" t="n">
-        <v>13039</v>
+        <v>16797</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3120</v>
+        <v>4435</v>
       </c>
       <c r="C4" t="n">
-        <v>7943</v>
+        <v>5967</v>
       </c>
       <c r="D4" t="n">
-        <v>8123</v>
+        <v>12575</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>2064</v>
       </c>
       <c r="C5" t="n">
-        <v>9651</v>
+        <v>7715</v>
       </c>
       <c r="D5" t="n">
-        <v>3084</v>
+        <v>4926</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>689</v>
+        <v>982</v>
       </c>
       <c r="C6" t="n">
-        <v>6803</v>
+        <v>5351</v>
       </c>
       <c r="D6" t="n">
-        <v>1005</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>4080</v>
+        <v>2349</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1602</v>
+        <v>802</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2413</v>
+        <v>5541</v>
       </c>
       <c r="C2" t="n">
-        <v>11298</v>
+        <v>5015</v>
       </c>
       <c r="D2" t="n">
-        <v>15815</v>
+        <v>13103</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2764</v>
+        <v>4309</v>
       </c>
       <c r="C3" t="n">
-        <v>4572</v>
+        <v>3143</v>
       </c>
       <c r="D3" t="n">
-        <v>11910</v>
+        <v>15417</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2981</v>
+        <v>4306</v>
       </c>
       <c r="C4" t="n">
-        <v>6944</v>
+        <v>5020</v>
       </c>
       <c r="D4" t="n">
-        <v>8631</v>
+        <v>12881</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>2657</v>
       </c>
       <c r="C5" t="n">
-        <v>8805</v>
+        <v>6839</v>
       </c>
       <c r="D5" t="n">
-        <v>3715</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>1272</v>
       </c>
       <c r="C6" t="n">
-        <v>7958</v>
+        <v>6352</v>
       </c>
       <c r="D6" t="n">
-        <v>1281</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
-        <v>5199</v>
+        <v>3600</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>2482</v>
+        <v>1378</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>735</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1671</v>
+        <v>3781</v>
       </c>
       <c r="C2" t="n">
-        <v>7069</v>
+        <v>2636</v>
       </c>
       <c r="D2" t="n">
-        <v>11502</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2332</v>
+        <v>4128</v>
       </c>
       <c r="C3" t="n">
-        <v>6519</v>
+        <v>3525</v>
       </c>
       <c r="D3" t="n">
-        <v>11718</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2665</v>
+        <v>3963</v>
       </c>
       <c r="C4" t="n">
-        <v>6022</v>
+        <v>4285</v>
       </c>
       <c r="D4" t="n">
-        <v>8860</v>
+        <v>12953</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2087</v>
+        <v>2979</v>
       </c>
       <c r="C5" t="n">
-        <v>8316</v>
+        <v>6295</v>
       </c>
       <c r="D5" t="n">
-        <v>4192</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>1509</v>
       </c>
       <c r="C6" t="n">
-        <v>8540</v>
+        <v>6769</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>6175</v>
+        <v>4519</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>3115</v>
+        <v>1864</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>801</v>
+        <v>515</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2456</v>
+        <v>6096</v>
       </c>
       <c r="C2" t="n">
-        <v>8322</v>
+        <v>4688</v>
       </c>
       <c r="D2" t="n">
-        <v>17863</v>
+        <v>10233</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1779</v>
+        <v>3370</v>
       </c>
       <c r="C3" t="n">
-        <v>6061</v>
+        <v>2810</v>
       </c>
       <c r="D3" t="n">
-        <v>10962</v>
+        <v>12871</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2219</v>
+        <v>3494</v>
       </c>
       <c r="C4" t="n">
-        <v>6097</v>
+        <v>3867</v>
       </c>
       <c r="D4" t="n">
-        <v>8974</v>
+        <v>12753</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2095</v>
+        <v>3047</v>
       </c>
       <c r="C5" t="n">
-        <v>7262</v>
+        <v>5334</v>
       </c>
       <c r="D5" t="n">
-        <v>4606</v>
+        <v>7291</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1259</v>
+        <v>1843</v>
       </c>
       <c r="C6" t="n">
-        <v>8389</v>
+        <v>6524</v>
       </c>
       <c r="D6" t="n">
-        <v>1796</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>641</v>
       </c>
       <c r="C7" t="n">
-        <v>7006</v>
+        <v>5421</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>4163</v>
+        <v>2799</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1503</v>
+        <v>969</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>393</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4137</v>
+        <v>7153</v>
       </c>
       <c r="C2" t="n">
-        <v>17826</v>
+        <v>2808</v>
       </c>
       <c r="D2" t="n">
-        <v>7156</v>
+        <v>14802</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1794</v>
+        <v>4361</v>
       </c>
       <c r="C2" t="n">
-        <v>4926</v>
+        <v>2663</v>
       </c>
       <c r="D2" t="n">
-        <v>13291</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2429</v>
+        <v>4509</v>
       </c>
       <c r="C3" t="n">
-        <v>7142</v>
+        <v>3488</v>
       </c>
       <c r="D3" t="n">
-        <v>12213</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3069</v>
+        <v>4606</v>
       </c>
       <c r="C4" t="n">
-        <v>8700</v>
+        <v>5647</v>
       </c>
       <c r="D4" t="n">
-        <v>9031</v>
+        <v>13065</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1182</v>
+        <v>1787</v>
       </c>
       <c r="C5" t="n">
-        <v>11272</v>
+        <v>8596</v>
       </c>
       <c r="D5" t="n">
-        <v>4213</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>387</v>
+        <v>592</v>
       </c>
       <c r="C6" t="n">
-        <v>8345</v>
+        <v>6591</v>
       </c>
       <c r="D6" t="n">
-        <v>1496</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>4079</v>
+        <v>2743</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1472</v>
+        <v>949</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7498</v>
+        <v>7135</v>
       </c>
       <c r="C2" t="n">
-        <v>8622</v>
+        <v>2732</v>
       </c>
       <c r="D2" t="n">
-        <v>10606</v>
+        <v>21785</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1759</v>
+        <v>3038</v>
       </c>
       <c r="C3" t="n">
-        <v>8984</v>
+        <v>1415</v>
       </c>
       <c r="D3" t="n">
-        <v>1841</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4748</v>
+        <v>4966</v>
       </c>
       <c r="C2" t="n">
-        <v>9238</v>
+        <v>6595</v>
       </c>
       <c r="D2" t="n">
-        <v>13899</v>
+        <v>22403</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3793</v>
+        <v>4179</v>
       </c>
       <c r="C3" t="n">
-        <v>7571</v>
+        <v>1862</v>
       </c>
       <c r="D3" t="n">
-        <v>3178</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>798</v>
+        <v>1353</v>
       </c>
       <c r="C4" t="n">
-        <v>5307</v>
+        <v>873</v>
       </c>
       <c r="D4" t="n">
-        <v>1552</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4489</v>
+        <v>6918</v>
       </c>
       <c r="C2" t="n">
-        <v>8605</v>
+        <v>7381</v>
       </c>
       <c r="D2" t="n">
-        <v>11434</v>
+        <v>23670</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3503</v>
+        <v>3762</v>
       </c>
       <c r="C3" t="n">
-        <v>7339</v>
+        <v>3845</v>
       </c>
       <c r="D3" t="n">
-        <v>4664</v>
+        <v>8215</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1911</v>
+        <v>2344</v>
       </c>
       <c r="C4" t="n">
-        <v>6457</v>
+        <v>1415</v>
       </c>
       <c r="D4" t="n">
-        <v>1817</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>383</v>
+        <v>616</v>
       </c>
       <c r="C5" t="n">
-        <v>2950</v>
+        <v>571</v>
       </c>
       <c r="D5" t="n">
-        <v>1226</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5116</v>
+        <v>6468</v>
       </c>
       <c r="C2" t="n">
-        <v>5055</v>
+        <v>10286</v>
       </c>
       <c r="D2" t="n">
-        <v>17942</v>
+        <v>20816</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3263</v>
+        <v>4299</v>
       </c>
       <c r="C3" t="n">
-        <v>6956</v>
+        <v>4989</v>
       </c>
       <c r="D3" t="n">
-        <v>5364</v>
+        <v>9985</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2284</v>
+        <v>2584</v>
       </c>
       <c r="C4" t="n">
-        <v>6788</v>
+        <v>2678</v>
       </c>
       <c r="D4" t="n">
-        <v>2281</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>918</v>
+        <v>1237</v>
       </c>
       <c r="C5" t="n">
-        <v>4644</v>
+        <v>1004</v>
       </c>
       <c r="D5" t="n">
-        <v>1290</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>232</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>1623</v>
+        <v>436</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6331</v>
+        <v>6651</v>
       </c>
       <c r="C2" t="n">
-        <v>17204</v>
+        <v>10574</v>
       </c>
       <c r="D2" t="n">
-        <v>19603</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3008</v>
+        <v>3913</v>
       </c>
       <c r="C3" t="n">
-        <v>4941</v>
+        <v>6343</v>
       </c>
       <c r="D3" t="n">
-        <v>6395</v>
+        <v>10282</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1713</v>
+        <v>2150</v>
       </c>
       <c r="C4" t="n">
-        <v>5568</v>
+        <v>3259</v>
       </c>
       <c r="D4" t="n">
-        <v>2370</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>813</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>4179</v>
+        <v>1383</v>
       </c>
       <c r="D5" t="n">
-        <v>1151</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>373</v>
       </c>
       <c r="C6" t="n">
-        <v>2067</v>
+        <v>484</v>
       </c>
       <c r="D6" t="n">
-        <v>744</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>614</v>
+        <v>252</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5073</v>
+        <v>6105</v>
       </c>
       <c r="C2" t="n">
-        <v>8432</v>
+        <v>8233</v>
       </c>
       <c r="D2" t="n">
-        <v>23245</v>
+        <v>35338</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3838</v>
+        <v>4386</v>
       </c>
       <c r="C3" t="n">
-        <v>10335</v>
+        <v>7606</v>
       </c>
       <c r="D3" t="n">
-        <v>8143</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2036</v>
+        <v>2664</v>
       </c>
       <c r="C4" t="n">
-        <v>5078</v>
+        <v>5086</v>
       </c>
       <c r="D4" t="n">
-        <v>3109</v>
+        <v>5173</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1120</v>
+        <v>1396</v>
       </c>
       <c r="C5" t="n">
-        <v>4892</v>
+        <v>2470</v>
       </c>
       <c r="D5" t="n">
-        <v>1339</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>641</v>
       </c>
       <c r="C6" t="n">
-        <v>3218</v>
+        <v>995</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>1411</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>428</v>
+        <v>238</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4192</v>
+        <v>5664</v>
       </c>
       <c r="C2" t="n">
-        <v>6992</v>
+        <v>5175</v>
       </c>
       <c r="D2" t="n">
-        <v>20805</v>
+        <v>34761</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>4298</v>
       </c>
       <c r="C3" t="n">
-        <v>8210</v>
+        <v>6879</v>
       </c>
       <c r="D3" t="n">
-        <v>9865</v>
+        <v>15661</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>3011</v>
       </c>
       <c r="C4" t="n">
-        <v>7749</v>
+        <v>6407</v>
       </c>
       <c r="D4" t="n">
-        <v>3902</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1377</v>
+        <v>1786</v>
       </c>
       <c r="C5" t="n">
-        <v>4888</v>
+        <v>3826</v>
       </c>
       <c r="D5" t="n">
-        <v>1621</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>714</v>
+        <v>919</v>
       </c>
       <c r="C6" t="n">
-        <v>4034</v>
+        <v>1776</v>
       </c>
       <c r="D6" t="n">
-        <v>891</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>379</v>
       </c>
       <c r="C7" t="n">
-        <v>2299</v>
+        <v>706</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>909</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>222</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_19_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6213</v>
+        <v>568</v>
       </c>
       <c r="C2" t="n">
-        <v>5174</v>
+        <v>3209</v>
       </c>
       <c r="D2" t="n">
-        <v>25444</v>
+        <v>18293</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4053</v>
+        <v>1073</v>
       </c>
       <c r="C3" t="n">
-        <v>5273</v>
+        <v>7712</v>
       </c>
       <c r="D3" t="n">
-        <v>17333</v>
+        <v>17066</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3084</v>
+        <v>854</v>
       </c>
       <c r="C4" t="n">
-        <v>6456</v>
+        <v>8291</v>
       </c>
       <c r="D4" t="n">
-        <v>7841</v>
+        <v>7381</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2085</v>
+        <v>504</v>
       </c>
       <c r="C5" t="n">
-        <v>5059</v>
+        <v>5612</v>
       </c>
       <c r="D5" t="n">
-        <v>3059</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1194</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>2760</v>
+        <v>2616</v>
       </c>
       <c r="D6" t="n">
-        <v>1262</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>558</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>1212</v>
+        <v>914</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>496</v>
+        <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9328</v>
+        <v>1254</v>
       </c>
       <c r="C2" t="n">
-        <v>6327</v>
+        <v>6614</v>
       </c>
       <c r="D2" t="n">
-        <v>26422</v>
+        <v>21231</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4090</v>
+        <v>711</v>
       </c>
       <c r="C3" t="n">
-        <v>4600</v>
+        <v>4769</v>
       </c>
       <c r="D3" t="n">
-        <v>17271</v>
+        <v>16051</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026</v>
+        <v>833</v>
       </c>
       <c r="C4" t="n">
-        <v>5753</v>
+        <v>7812</v>
       </c>
       <c r="D4" t="n">
-        <v>9151</v>
+        <v>8923</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2226</v>
+        <v>589</v>
       </c>
       <c r="C5" t="n">
-        <v>5548</v>
+        <v>6912</v>
       </c>
       <c r="D5" t="n">
-        <v>3671</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1435</v>
+        <v>319</v>
       </c>
       <c r="C6" t="n">
-        <v>3770</v>
+        <v>4052</v>
       </c>
       <c r="D6" t="n">
-        <v>1521</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>749</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>1882</v>
+        <v>1706</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>312</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>804</v>
+        <v>604</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12405</v>
+        <v>672</v>
       </c>
       <c r="C2" t="n">
-        <v>6206</v>
+        <v>2835</v>
       </c>
       <c r="D2" t="n">
-        <v>25182</v>
+        <v>14448</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4996</v>
+        <v>833</v>
       </c>
       <c r="C3" t="n">
-        <v>4712</v>
+        <v>5279</v>
       </c>
       <c r="D3" t="n">
-        <v>17475</v>
+        <v>16261</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2948</v>
+        <v>905</v>
       </c>
       <c r="C4" t="n">
-        <v>5124</v>
+        <v>7335</v>
       </c>
       <c r="D4" t="n">
-        <v>9954</v>
+        <v>9832</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2270</v>
+        <v>607</v>
       </c>
       <c r="C5" t="n">
-        <v>5465</v>
+        <v>8067</v>
       </c>
       <c r="D5" t="n">
-        <v>4313</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1615</v>
+        <v>264</v>
       </c>
       <c r="C6" t="n">
-        <v>4470</v>
+        <v>4973</v>
       </c>
       <c r="D6" t="n">
-        <v>1810</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>914</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2621</v>
+        <v>1577</v>
       </c>
       <c r="D7" t="n">
-        <v>843</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>424</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>525</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10999</v>
+        <v>476</v>
       </c>
       <c r="C2" t="n">
-        <v>4220</v>
+        <v>5912</v>
       </c>
       <c r="D2" t="n">
-        <v>20816</v>
+        <v>17411</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5704</v>
+        <v>648</v>
       </c>
       <c r="C3" t="n">
-        <v>7334</v>
+        <v>3606</v>
       </c>
       <c r="D3" t="n">
-        <v>19162</v>
+        <v>14881</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2097</v>
+        <v>768</v>
       </c>
       <c r="C4" t="n">
-        <v>8099</v>
+        <v>6206</v>
       </c>
       <c r="D4" t="n">
-        <v>9479</v>
+        <v>10644</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>670</v>
       </c>
       <c r="C5" t="n">
-        <v>4380</v>
+        <v>7625</v>
       </c>
       <c r="D5" t="n">
-        <v>2933</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>844</v>
+        <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>2568</v>
+        <v>6417</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>1193</v>
+        <v>3022</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>514</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6398</v>
+        <v>274</v>
       </c>
       <c r="C2" t="n">
-        <v>1810</v>
+        <v>3977</v>
       </c>
       <c r="D2" t="n">
-        <v>14374</v>
+        <v>12741</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6766</v>
+        <v>514</v>
       </c>
       <c r="C3" t="n">
-        <v>5346</v>
+        <v>4186</v>
       </c>
       <c r="D3" t="n">
-        <v>18283</v>
+        <v>14371</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3040</v>
+        <v>672</v>
       </c>
       <c r="C4" t="n">
-        <v>7881</v>
+        <v>5107</v>
       </c>
       <c r="D4" t="n">
-        <v>10860</v>
+        <v>11032</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1632</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>6034</v>
+        <v>7200</v>
       </c>
       <c r="D5" t="n">
-        <v>3717</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1012</v>
+        <v>430</v>
       </c>
       <c r="C6" t="n">
-        <v>3325</v>
+        <v>7089</v>
       </c>
       <c r="D6" t="n">
-        <v>1042</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>1675</v>
+        <v>4159</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>700</v>
+        <v>1428</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6990</v>
+        <v>681</v>
       </c>
       <c r="C2" t="n">
-        <v>6187</v>
+        <v>4761</v>
       </c>
       <c r="D2" t="n">
-        <v>21631</v>
+        <v>12094</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5544</v>
+        <v>354</v>
       </c>
       <c r="C3" t="n">
-        <v>3216</v>
+        <v>3616</v>
       </c>
       <c r="D3" t="n">
-        <v>16637</v>
+        <v>13219</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4001</v>
+        <v>537</v>
       </c>
       <c r="C4" t="n">
-        <v>6527</v>
+        <v>4576</v>
       </c>
       <c r="D4" t="n">
-        <v>11741</v>
+        <v>11209</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1975</v>
+        <v>622</v>
       </c>
       <c r="C5" t="n">
-        <v>6777</v>
+        <v>6125</v>
       </c>
       <c r="D5" t="n">
-        <v>4665</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1169</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>4514</v>
+        <v>7140</v>
       </c>
       <c r="D6" t="n">
-        <v>1438</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>549</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>2418</v>
+        <v>5334</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1107</v>
+        <v>2485</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>782</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4135</v>
+        <v>468</v>
       </c>
       <c r="C2" t="n">
-        <v>2841</v>
+        <v>2589</v>
       </c>
       <c r="D2" t="n">
-        <v>14952</v>
+        <v>8804</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5683</v>
+        <v>538</v>
       </c>
       <c r="C3" t="n">
-        <v>4135</v>
+        <v>4204</v>
       </c>
       <c r="D3" t="n">
-        <v>16797</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4435</v>
+        <v>837</v>
       </c>
       <c r="C4" t="n">
-        <v>5967</v>
+        <v>6584</v>
       </c>
       <c r="D4" t="n">
-        <v>12575</v>
+        <v>11393</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2064</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>7715</v>
+        <v>9562</v>
       </c>
       <c r="D5" t="n">
-        <v>4926</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>982</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>5351</v>
+        <v>6836</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>2349</v>
+        <v>2435</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>802</v>
+        <v>766</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5541</v>
+        <v>228</v>
       </c>
       <c r="C2" t="n">
-        <v>5015</v>
+        <v>2146</v>
       </c>
       <c r="D2" t="n">
-        <v>13103</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4309</v>
+        <v>432</v>
       </c>
       <c r="C3" t="n">
-        <v>3143</v>
+        <v>3042</v>
       </c>
       <c r="D3" t="n">
-        <v>15417</v>
+        <v>12473</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4306</v>
+        <v>583</v>
       </c>
       <c r="C4" t="n">
-        <v>5020</v>
+        <v>5127</v>
       </c>
       <c r="D4" t="n">
-        <v>12881</v>
+        <v>11025</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2657</v>
+        <v>448</v>
       </c>
       <c r="C5" t="n">
-        <v>6839</v>
+        <v>7209</v>
       </c>
       <c r="D5" t="n">
-        <v>5998</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>177</v>
       </c>
       <c r="C6" t="n">
-        <v>6352</v>
+        <v>6598</v>
       </c>
       <c r="D6" t="n">
-        <v>1858</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>3600</v>
+        <v>3050</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1378</v>
+        <v>885</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3781</v>
+        <v>141</v>
       </c>
       <c r="C2" t="n">
-        <v>2636</v>
+        <v>5387</v>
       </c>
       <c r="D2" t="n">
-        <v>10024</v>
+        <v>15236</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4128</v>
+        <v>284</v>
       </c>
       <c r="C3" t="n">
-        <v>3525</v>
+        <v>2234</v>
       </c>
       <c r="D3" t="n">
-        <v>14300</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3963</v>
+        <v>447</v>
       </c>
       <c r="C4" t="n">
-        <v>4285</v>
+        <v>3928</v>
       </c>
       <c r="D4" t="n">
-        <v>12953</v>
+        <v>10953</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2979</v>
+        <v>462</v>
       </c>
       <c r="C5" t="n">
-        <v>6295</v>
+        <v>5979</v>
       </c>
       <c r="D5" t="n">
-        <v>6723</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1509</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>6769</v>
+        <v>6896</v>
       </c>
       <c r="D6" t="n">
-        <v>2229</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>4519</v>
+        <v>4752</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1864</v>
+        <v>1890</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6096</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>4688</v>
+        <v>9428</v>
       </c>
       <c r="D2" t="n">
-        <v>10233</v>
+        <v>17176</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3370</v>
+        <v>186</v>
       </c>
       <c r="C3" t="n">
-        <v>2810</v>
+        <v>3270</v>
       </c>
       <c r="D3" t="n">
-        <v>12871</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3494</v>
+        <v>328</v>
       </c>
       <c r="C4" t="n">
-        <v>3867</v>
+        <v>3000</v>
       </c>
       <c r="D4" t="n">
-        <v>12753</v>
+        <v>10607</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3047</v>
+        <v>416</v>
       </c>
       <c r="C5" t="n">
-        <v>5334</v>
+        <v>4870</v>
       </c>
       <c r="D5" t="n">
-        <v>7291</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1843</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>6524</v>
+        <v>6404</v>
       </c>
       <c r="D6" t="n">
-        <v>2804</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>641</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>5421</v>
+        <v>5716</v>
       </c>
       <c r="D7" t="n">
-        <v>977</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>2799</v>
+        <v>3104</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>969</v>
+        <v>1106</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7153</v>
+        <v>3808</v>
       </c>
       <c r="C2" t="n">
-        <v>2808</v>
+        <v>17381</v>
       </c>
       <c r="D2" t="n">
-        <v>14802</v>
+        <v>9374</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4361</v>
+        <v>319</v>
       </c>
       <c r="C2" t="n">
-        <v>2663</v>
+        <v>21715</v>
       </c>
       <c r="D2" t="n">
-        <v>7531</v>
+        <v>20820</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4509</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>3488</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>13868</v>
+        <v>10873</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4606</v>
+        <v>235</v>
       </c>
       <c r="C4" t="n">
-        <v>5647</v>
+        <v>3059</v>
       </c>
       <c r="D4" t="n">
-        <v>13065</v>
+        <v>10307</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1787</v>
+        <v>352</v>
       </c>
       <c r="C5" t="n">
-        <v>8596</v>
+        <v>3914</v>
       </c>
       <c r="D5" t="n">
-        <v>6693</v>
+        <v>7086</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>6591</v>
+        <v>5697</v>
       </c>
       <c r="D6" t="n">
-        <v>2206</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>5940</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>949</v>
+        <v>4152</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>1869</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>603</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7135</v>
+        <v>3399</v>
       </c>
       <c r="C2" t="n">
-        <v>2732</v>
+        <v>10547</v>
       </c>
       <c r="D2" t="n">
-        <v>21785</v>
+        <v>29441</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3038</v>
+        <v>1229</v>
       </c>
       <c r="C3" t="n">
-        <v>1415</v>
+        <v>6863</v>
       </c>
       <c r="D3" t="n">
-        <v>3126</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4966</v>
+        <v>2029</v>
       </c>
       <c r="C2" t="n">
-        <v>6595</v>
+        <v>6559</v>
       </c>
       <c r="D2" t="n">
-        <v>22403</v>
+        <v>24252</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4179</v>
+        <v>1960</v>
       </c>
       <c r="C3" t="n">
-        <v>1862</v>
+        <v>7771</v>
       </c>
       <c r="D3" t="n">
-        <v>6030</v>
+        <v>6602</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1353</v>
+        <v>584</v>
       </c>
       <c r="C4" t="n">
-        <v>873</v>
+        <v>4265</v>
       </c>
       <c r="D4" t="n">
-        <v>1811</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6918</v>
+        <v>1302</v>
       </c>
       <c r="C2" t="n">
-        <v>7381</v>
+        <v>5622</v>
       </c>
       <c r="D2" t="n">
-        <v>23670</v>
+        <v>33159</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3762</v>
+        <v>1646</v>
       </c>
       <c r="C3" t="n">
-        <v>3845</v>
+        <v>6110</v>
       </c>
       <c r="D3" t="n">
-        <v>8215</v>
+        <v>9081</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2344</v>
+        <v>1105</v>
       </c>
       <c r="C4" t="n">
-        <v>1415</v>
+        <v>6229</v>
       </c>
       <c r="D4" t="n">
-        <v>2565</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>616</v>
+        <v>291</v>
       </c>
       <c r="C5" t="n">
-        <v>571</v>
+        <v>2501</v>
       </c>
       <c r="D5" t="n">
-        <v>1252</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6468</v>
+        <v>1055</v>
       </c>
       <c r="C2" t="n">
-        <v>10286</v>
+        <v>3802</v>
       </c>
       <c r="D2" t="n">
-        <v>20816</v>
+        <v>28330</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4299</v>
+        <v>1229</v>
       </c>
       <c r="C3" t="n">
-        <v>4989</v>
+        <v>5072</v>
       </c>
       <c r="D3" t="n">
-        <v>9985</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2584</v>
+        <v>1172</v>
       </c>
       <c r="C4" t="n">
-        <v>2678</v>
+        <v>6033</v>
       </c>
       <c r="D4" t="n">
-        <v>3492</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1237</v>
+        <v>590</v>
       </c>
       <c r="C5" t="n">
-        <v>1004</v>
+        <v>4453</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>436</v>
+        <v>1420</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6651</v>
+        <v>1178</v>
       </c>
       <c r="C2" t="n">
-        <v>10574</v>
+        <v>7821</v>
       </c>
       <c r="D2" t="n">
-        <v>30300</v>
+        <v>29954</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3913</v>
+        <v>955</v>
       </c>
       <c r="C3" t="n">
-        <v>6343</v>
+        <v>3912</v>
       </c>
       <c r="D3" t="n">
-        <v>10282</v>
+        <v>13972</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2150</v>
+        <v>1030</v>
       </c>
       <c r="C4" t="n">
-        <v>3259</v>
+        <v>5351</v>
       </c>
       <c r="D4" t="n">
-        <v>3958</v>
+        <v>5011</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>755</v>
       </c>
       <c r="C5" t="n">
-        <v>1383</v>
+        <v>5164</v>
       </c>
       <c r="D5" t="n">
-        <v>1443</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>484</v>
+        <v>2889</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>252</v>
+        <v>835</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>296</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6105</v>
+        <v>1142</v>
       </c>
       <c r="C2" t="n">
-        <v>8233</v>
+        <v>13349</v>
       </c>
       <c r="D2" t="n">
-        <v>35338</v>
+        <v>34083</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4386</v>
+        <v>867</v>
       </c>
       <c r="C3" t="n">
-        <v>7606</v>
+        <v>5031</v>
       </c>
       <c r="D3" t="n">
-        <v>13031</v>
+        <v>15206</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2664</v>
+        <v>859</v>
       </c>
       <c r="C4" t="n">
-        <v>5086</v>
+        <v>4535</v>
       </c>
       <c r="D4" t="n">
-        <v>5173</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1396</v>
+        <v>778</v>
       </c>
       <c r="C5" t="n">
-        <v>2470</v>
+        <v>5094</v>
       </c>
       <c r="D5" t="n">
-        <v>1906</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>641</v>
+        <v>465</v>
       </c>
       <c r="C6" t="n">
-        <v>995</v>
+        <v>3908</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>383</v>
+        <v>1760</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>238</v>
+        <v>525</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5664</v>
+        <v>1068</v>
       </c>
       <c r="C2" t="n">
-        <v>5175</v>
+        <v>8436</v>
       </c>
       <c r="D2" t="n">
-        <v>34761</v>
+        <v>27159</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4298</v>
+        <v>1315</v>
       </c>
       <c r="C3" t="n">
-        <v>6879</v>
+        <v>8683</v>
       </c>
       <c r="D3" t="n">
-        <v>15661</v>
+        <v>16511</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3011</v>
+        <v>718</v>
       </c>
       <c r="C4" t="n">
-        <v>6407</v>
+        <v>7633</v>
       </c>
       <c r="D4" t="n">
-        <v>6524</v>
+        <v>5677</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1786</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>3826</v>
+        <v>3829</v>
       </c>
       <c r="D5" t="n">
-        <v>2425</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>1776</v>
+        <v>1724</v>
       </c>
       <c r="D6" t="n">
-        <v>1066</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>706</v>
+        <v>514</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
